--- a/data/trans_orig/IP07_C16_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C16_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han sufrido cyberbulling en 2023 (tasa de respuesta: 99,48%)</t>
+          <t>Menores según si han sufrido cyberbulling en su colegio/instituto o fuera de él en 2023 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>91444</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>85361</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>94994</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>92,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,64%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>64704</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>60313</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>66747</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92000</t>
+          <t>68243</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85979</t>
+          <t>63954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95674</t>
+          <t>70415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>156704</t>
+          <t>159688</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150177</t>
+          <t>152558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161024</t>
+          <t>164128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>752</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4598</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4668</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>752</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4541</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7075</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13158</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,36%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2078</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5795</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2196</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6608</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,08%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7365</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3691</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13386</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>67534</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>67534</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>67534</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>71266</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>71266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>71266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>166899</t>
+          <t>169785</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166899</t>
+          <t>169785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166899</t>
+          <t>169785</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>163651</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145555</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>168942</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>108013</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>60083</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>135434</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>163954</t>
+          <t>115419</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147998</t>
+          <t>105882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169997</t>
+          <t>120216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>271968</t>
+          <t>279070</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>192331</t>
+          <t>261388</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>301463</t>
+          <t>286445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1289,107 +1289,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22773</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28620</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1488</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>79816</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>20,18%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4464</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>17085</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>9723</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>31786</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>56,27%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>22350</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>34759</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>114515</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5204</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10144</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170704</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>170704</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>170704</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>141837</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>141837</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141837</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>171962</t>
+          <t>125176</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171962</t>
+          <t>125176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171962</t>
+          <t>125176</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>313799</t>
+          <t>295880</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313799</t>
+          <t>295880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313799</t>
+          <t>295880</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>255095</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>240135</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>261993</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>89,2%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>172717</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>111625</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>199742</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>255953</t>
+          <t>183661</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>234539</t>
+          <t>172982</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>262989</t>
+          <t>189085</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>428671</t>
+          <t>438757</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>340510</t>
+          <t>421382</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>459204</t>
+          <t>448408</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24872</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>29372</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>91786</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128736</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15630</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7281</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13710</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
